--- a/reports/빅딜/history/2026-04-10/빅딜_mgf_matched_5_guilds.xlsx
+++ b/reports/빅딜/history/2026-04-10/빅딜_mgf_matched_5_guilds.xlsx
@@ -1577,7 +1577,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%96%80%EB%AC%BC%EA%B0%9C</t>
   </si>
   <si>
-    <t>5874억 4080만</t>
+    <t>5980억 8056만</t>
   </si>
   <si>
     <t>초코냥부하</t>
@@ -1667,7 +1667,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EA%B0%80%EB%82%9C%EA%BD%9D%EC%84%AD%EC%9D%B4</t>
   </si>
   <si>
-    <t>1713억 1425만</t>
+    <t>1715억 9218만</t>
   </si>
   <si>
     <t>이진니</t>
